--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44455</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44476</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44784</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>44723</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1508,6 +1508,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44951</v>
+        <v>45631</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44978</v>
+        <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>14.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45534</v>
+        <v>45698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45554</v>
+        <v>45608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1856,14 +1861,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44596</v>
+        <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45547</v>
+        <v>45631</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45827</v>
+        <v>44887</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>18.7</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45827</v>
+        <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44977</v>
+        <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>18.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45616</v>
+        <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44837</v>
+        <v>44977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45628</v>
+        <v>46058</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45608</v>
+        <v>46058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44992</v>
+        <v>45616</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2586,14 +2591,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46084</v>
+        <v>45497</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2605,13 +2610,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45027</v>
+        <v>45607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2737,14 +2737,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45219</v>
+        <v>46084</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2754,6 +2754,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45287</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2829,13 +2834,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45621</v>
+        <v>44951</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45497</v>
+        <v>44978</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44937</v>
+        <v>45546</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45338</v>
+        <v>44978</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
         <v>45758</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46058</v>
+        <v>45173</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46058</v>
+        <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45608</v>
+        <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>14.7</v>
+        <v>0.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45068</v>
+        <v>45684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45545</v>
+        <v>44951</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45545</v>
+        <v>46023</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45631</v>
+        <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45684</v>
+        <v>46205</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45684</v>
+        <v>45068</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45658</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44816</v>
+        <v>46210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45607</v>
+        <v>45098</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45225</v>
+        <v>46252</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45187</v>
+        <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46023</v>
+        <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45173</v>
+        <v>45658</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45314</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45237</v>
+        <v>45314</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45631</v>
+        <v>46223</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45628</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44887</v>
+        <v>46223</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>6.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44951</v>
+        <v>45404</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45098</v>
+        <v>44977</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45404</v>
+        <v>45628</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>44992</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45546</v>
+        <v>44783</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46252</v>
+        <v>45295</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46210</v>
+        <v>45187</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>45322</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45322</v>
+        <v>45534</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44977</v>
+        <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46218</v>
+        <v>44596</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45295</v>
+        <v>45621</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46223</v>
+        <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46223</v>
+        <v>44784</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44784</v>
+        <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6034,7 +6034,7 @@
         <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44978</v>
+        <v>44937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45019</v>
+        <v>45287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,8 +6192,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6236,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6250,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45454</v>
+        <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6265,13 +6270,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45632</v>
+        <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45698</v>
+        <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6470,14 +6470,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45791</v>
+        <v>45632</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44455</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44474</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44476</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44784</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44723</v>
+        <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45454</v>
+        <v>44723</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1510,13 +1510,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45631</v>
+        <v>45187</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45608</v>
+        <v>45173</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45698</v>
+        <v>44783</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45608</v>
+        <v>45314</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1861,14 +1856,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45791</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45631</v>
+        <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2007,14 +2002,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44887</v>
+        <v>46084</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2026,8 +2021,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44837</v>
+        <v>44978</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45827</v>
+        <v>45631</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>18.7</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45827</v>
+        <v>44837</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44977</v>
+        <v>45534</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46058</v>
+        <v>45628</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46058</v>
+        <v>45554</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45616</v>
+        <v>44596</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45497</v>
+        <v>45547</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45607</v>
+        <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2737,14 +2737,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46084</v>
+        <v>45628</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2756,13 +2756,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45758</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44951</v>
+        <v>45608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44978</v>
+        <v>44887</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45546</v>
+        <v>44951</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44978</v>
+        <v>44992</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3170,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3180,14 +3175,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45758</v>
+        <v>45098</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45173</v>
+        <v>45404</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45684</v>
+        <v>45027</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45545</v>
+        <v>45684</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45684</v>
+        <v>45219</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44951</v>
+        <v>45684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3608,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46023</v>
+        <v>45287</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3637,8 +3632,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46185</v>
+        <v>45621</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46205</v>
+        <v>45546</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45068</v>
+        <v>45497</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46210</v>
+        <v>46023</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45098</v>
+        <v>45338</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46252</v>
+        <v>46058</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46210</v>
+        <v>46058</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45027</v>
+        <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45658</v>
+        <v>45322</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45338</v>
+        <v>44977</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45314</v>
+        <v>45608</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>14.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46218</v>
+        <v>45068</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46223</v>
+        <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45628</v>
+        <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46223</v>
+        <v>46205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45404</v>
+        <v>45631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44977</v>
+        <v>45295</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45628</v>
+        <v>46252</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44992</v>
+        <v>45658</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44783</v>
+        <v>46210</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45295</v>
+        <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45187</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44816</v>
+        <v>45607</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45322</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45534</v>
+        <v>46218</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45219</v>
+        <v>44784</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44596</v>
+        <v>46223</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45621</v>
+        <v>46223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45019</v>
+        <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44784</v>
+        <v>44978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45554</v>
+        <v>45019</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45545</v>
+        <v>45454</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6046,8 +6046,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44937</v>
+        <v>45632</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45287</v>
+        <v>45698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,13 +6197,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6251,14 +6251,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45225</v>
+        <v>45791</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45545</v>
+        <v>45827</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.2</v>
+        <v>18.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45547</v>
+        <v>45827</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6460,7 +6460,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45632</v>
+        <v>45616</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE80"/>
+  <dimension ref="A1:AE79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 49616-2021</t>
+          <t>A 55146-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44455</v>
+        <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55146-2021</t>
+          <t>A 55757-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44474</v>
+        <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 55757-2021</t>
+          <t>A 55760-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 55760-2021</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44476</v>
+        <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44784</v>
+        <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45225</v>
+        <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,8 +1437,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44723</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45187</v>
+        <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>14.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45173</v>
+        <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44783</v>
+        <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45314</v>
+        <v>44887</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1856,14 +1861,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44951</v>
+        <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2002,14 +2007,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46084</v>
+        <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2021,13 +2026,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>18.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44978</v>
+        <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.1</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45631</v>
+        <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44837</v>
+        <v>45497</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45534</v>
+        <v>45607</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45628</v>
+        <v>45616</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45554</v>
+        <v>46058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44596</v>
+        <v>46058</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45547</v>
+        <v>45237</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44977</v>
+        <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45628</v>
+        <v>44978</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45758</v>
+        <v>45546</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45608</v>
+        <v>46084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,8 +2902,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44887</v>
+        <v>44978</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44951</v>
+        <v>45173</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44992</v>
+        <v>45545</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3165,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3175,14 +3180,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45098</v>
+        <v>44951</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45404</v>
+        <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3321,14 +3326,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45027</v>
+        <v>45098</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45684</v>
+        <v>45027</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45219</v>
+        <v>45658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45684</v>
+        <v>45338</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45287</v>
+        <v>45314</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3632,13 +3637,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45621</v>
+        <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45546</v>
+        <v>45404</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45497</v>
+        <v>44977</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>45758</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46023</v>
+        <v>45628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45338</v>
+        <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46058</v>
+        <v>44992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46058</v>
+        <v>44783</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46185</v>
+        <v>45684</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45322</v>
+        <v>45295</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44977</v>
+        <v>45187</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45608</v>
+        <v>44816</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>14.7</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45068</v>
+        <v>46023</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45545</v>
+        <v>45322</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45545</v>
+        <v>45534</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46205</v>
+        <v>45219</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45631</v>
+        <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45295</v>
+        <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46252</v>
+        <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45658</v>
+        <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>46210</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44816</v>
+        <v>46210</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45607</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>45019</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46218</v>
+        <v>44784</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44784</v>
+        <v>45554</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5742,7 +5742,7 @@
         <v>46223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45545</v>
+        <v>46223</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.1</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44978</v>
+        <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45019</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45454</v>
+        <v>45287</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45632</v>
+        <v>45225</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45698</v>
+        <v>45545</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6251,14 +6251,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45791</v>
+        <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45827</v>
+        <v>45632</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>18.7</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
       </c>
       <c r="V78" s="2" t="inlineStr"/>
     </row>
-    <row r="79" ht="15" customHeight="1">
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45827</v>
+        <v>45698</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6456,79 +6456,6 @@
         <v>0</v>
       </c>
       <c r="V79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>A 54080-2024</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>45616</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45454</v>
+        <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1435,11 +1435,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>44951</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45608</v>
+        <v>44978</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14.7</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45608</v>
+        <v>45534</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45631</v>
+        <v>45554</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44887</v>
+        <v>44596</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1861,14 +1856,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45791</v>
+        <v>45547</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44977</v>
+        <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>18.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2014,7 +2009,7 @@
         <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>18.7</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44837</v>
+        <v>44977</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2153,14 +2148,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45827</v>
+        <v>46084</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2172,8 +2167,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45497</v>
+        <v>45616</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45607</v>
+        <v>45628</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45616</v>
+        <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46058</v>
+        <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46058</v>
+        <v>44837</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45237</v>
+        <v>45027</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44951</v>
+        <v>45219</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2756,8 +2756,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45546</v>
+        <v>45621</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2883,14 +2888,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46084</v>
+        <v>45758</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,13 +2907,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44978</v>
+        <v>45497</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45173</v>
+        <v>44937</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45545</v>
+        <v>45338</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44951</v>
+        <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45068</v>
+        <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45098</v>
+        <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>14.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45027</v>
+        <v>45068</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45338</v>
+        <v>45545</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45314</v>
+        <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45628</v>
+        <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45404</v>
+        <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44977</v>
+        <v>45658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45758</v>
+        <v>44816</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45628</v>
+        <v>45607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45684</v>
+        <v>46205</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44992</v>
+        <v>45225</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44783</v>
+        <v>46252</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45684</v>
+        <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45295</v>
+        <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>45187</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44816</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46023</v>
+        <v>45173</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45322</v>
+        <v>45314</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45534</v>
+        <v>45237</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45219</v>
+        <v>46218</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46185</v>
+        <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44596</v>
+        <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45621</v>
+        <v>45631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>45628</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46210</v>
+        <v>44887</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46210</v>
+        <v>44951</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46252</v>
+        <v>45098</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>45404</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>45546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44784</v>
+        <v>45322</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45554</v>
+        <v>44977</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46218</v>
+        <v>46058</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46223</v>
+        <v>46058</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46223</v>
+        <v>45295</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45545</v>
+        <v>44784</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44937</v>
+        <v>45545</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45287</v>
+        <v>44978</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6046,13 +6046,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45225</v>
+        <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45545</v>
+        <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6197,8 +6192,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45547</v>
+        <v>45632</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45632</v>
+        <v>45698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45698</v>
+        <v>45791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44951</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44978</v>
+        <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>14.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45534</v>
+        <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45554</v>
+        <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44596</v>
+        <v>44887</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45547</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45827</v>
+        <v>45497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>18.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45827</v>
+        <v>45607</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44977</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2148,14 +2153,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46084</v>
+        <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2167,13 +2172,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45616</v>
+        <v>44978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45628</v>
+        <v>45546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45608</v>
+        <v>44837</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44992</v>
+        <v>44978</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44837</v>
+        <v>45758</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45027</v>
+        <v>45173</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45219</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45287</v>
+        <v>44951</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2754,11 +2754,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45621</v>
+        <v>45684</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45758</v>
+        <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2961,14 +2956,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45497</v>
+        <v>45098</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44937</v>
+        <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45338</v>
+        <v>45684</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45684</v>
+        <v>45658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45684</v>
+        <v>45338</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45608</v>
+        <v>45314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45068</v>
+        <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46023</v>
+        <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45545</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45545</v>
+        <v>45628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3681,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46185</v>
+        <v>44992</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45631</v>
+        <v>44783</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45658</v>
+        <v>45295</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44816</v>
+        <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45607</v>
+        <v>46058</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46205</v>
+        <v>46058</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45225</v>
+        <v>46023</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46252</v>
+        <v>44816</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46210</v>
+        <v>45322</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46210</v>
+        <v>45534</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45187</v>
+        <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46210</v>
+        <v>46185</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4567,14 +4562,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45173</v>
+        <v>46084</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4586,8 +4581,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45314</v>
+        <v>44596</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45237</v>
+        <v>45621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46218</v>
+        <v>45019</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46223</v>
+        <v>44784</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46223</v>
+        <v>46205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45631</v>
+        <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45628</v>
+        <v>46210</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44887</v>
+        <v>45554</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44951</v>
+        <v>46252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45098</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45404</v>
+        <v>45545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45546</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45322</v>
+        <v>45287</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5535,8 +5535,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44977</v>
+        <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46058</v>
+        <v>46218</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46058</v>
+        <v>46223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45295</v>
+        <v>46223</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45545</v>
+        <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44978</v>
+        <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45019</v>
+        <v>45698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6173,14 +6178,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45454</v>
+        <v>45791</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6190,11 +6195,6 @@
       <c r="G76" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45632</v>
+        <v>45827</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>18.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45698</v>
+        <v>45827</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6397,14 +6397,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45791</v>
+        <v>45616</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44887</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45607</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44837</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44978</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45758</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45173</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>44951</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45684</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45098</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45684</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45338</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44992</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44783</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45295</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46058</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46058</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46023</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>44816</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45322</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45534</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46185</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>46084</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44596</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45019</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44784</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46210</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45554</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45287</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>46218</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>46223</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45791</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45827</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45827</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45616</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44887</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45607</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44951</v>
+        <v>44837</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44978</v>
+        <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45546</v>
+        <v>44978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44837</v>
+        <v>45546</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44978</v>
+        <v>45758</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45758</v>
+        <v>45684</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45173</v>
+        <v>45684</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>44978</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44951</v>
+        <v>45173</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45684</v>
+        <v>45545</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45068</v>
+        <v>44951</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2956,14 +2956,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45098</v>
+        <v>45068</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45027</v>
+        <v>45098</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45684</v>
+        <v>45027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>45658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45338</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45628</v>
+        <v>46023</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45404</v>
+        <v>45628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44977</v>
+        <v>46185</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45628</v>
+        <v>45404</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44992</v>
+        <v>44977</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44783</v>
+        <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45295</v>
+        <v>46058</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45187</v>
+        <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46058</v>
+        <v>44992</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46058</v>
+        <v>44783</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46023</v>
+        <v>46084</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4143,8 +4143,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44816</v>
+        <v>45295</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45322</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45534</v>
+        <v>44816</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45219</v>
+        <v>45322</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46185</v>
+        <v>45534</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4562,14 +4567,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46084</v>
+        <v>46205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4581,13 +4586,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44596</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45621</v>
+        <v>45219</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45019</v>
+        <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44784</v>
+        <v>46252</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>44596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45554</v>
+        <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46252</v>
+        <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45545</v>
+        <v>45019</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>44784</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45287</v>
+        <v>45554</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5535,13 +5535,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45225</v>
+        <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46218</v>
+        <v>44937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46223</v>
+        <v>45287</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5759,8 +5754,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46223</v>
+        <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45791</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45827</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45827</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45616</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44784</v>
+        <v>45632</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45454</v>
+        <v>45027</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,13 +1437,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>44784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45608</v>
+        <v>44783</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14.7</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45608</v>
+        <v>45219</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45631</v>
+        <v>45287</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1734,8 +1729,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44887</v>
+        <v>45621</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>45497</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45497</v>
+        <v>45698</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45607</v>
+        <v>44937</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45338</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>44837</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2306,7 +2306,7 @@
         <v>44978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45546</v>
+        <v>45534</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45758</v>
+        <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>14.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45684</v>
+        <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2591,14 +2591,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45684</v>
+        <v>45791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44978</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45173</v>
+        <v>45545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45545</v>
+        <v>45631</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44951</v>
+        <v>45554</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45068</v>
+        <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45098</v>
+        <v>45547</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45027</v>
+        <v>45658</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45658</v>
+        <v>44816</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45338</v>
+        <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45314</v>
+        <v>45607</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46023</v>
+        <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45628</v>
+        <v>45608</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46185</v>
+        <v>45225</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45404</v>
+        <v>44992</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.2</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44977</v>
+        <v>45827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>18.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46058</v>
+        <v>45827</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46058</v>
+        <v>45187</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45628</v>
+        <v>45173</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44992</v>
+        <v>45314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44783</v>
+        <v>45237</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46084</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4143,13 +4143,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45295</v>
+        <v>45628</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>46058</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44816</v>
+        <v>46058</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45322</v>
+        <v>44887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45534</v>
+        <v>44951</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4567,14 +4562,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46205</v>
+        <v>45098</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4640,14 +4635,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46210</v>
+        <v>46084</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4659,8 +4654,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45219</v>
+        <v>45404</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46210</v>
+        <v>45616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46252</v>
+        <v>45546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46210</v>
+        <v>45322</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44596</v>
+        <v>44977</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46218</v>
+        <v>45295</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45621</v>
+        <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46223</v>
+        <v>45758</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46223</v>
+        <v>45545</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>0.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45019</v>
+        <v>44978</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44784</v>
+        <v>45019</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45554</v>
+        <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5535,8 +5535,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45545</v>
+        <v>45684</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44937</v>
+        <v>45684</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45287</v>
+        <v>46023</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5754,13 +5759,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45225</v>
+        <v>46185</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45545</v>
+        <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45547</v>
+        <v>46252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45632</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45698</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6178,14 +6178,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45791</v>
+        <v>46210</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45827</v>
+        <v>46218</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>18.7</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45827</v>
+        <v>46223</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45616</v>
+        <v>46223</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45632</v>
+        <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45027</v>
+        <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,8 +1437,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44784</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44783</v>
+        <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>14.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45219</v>
+        <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45287</v>
+        <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1729,13 +1734,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45621</v>
+        <v>44887</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45497</v>
+        <v>44977</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45698</v>
+        <v>45497</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44937</v>
+        <v>45607</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45338</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>44837</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2306,7 +2306,7 @@
         <v>44978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45534</v>
+        <v>45546</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45608</v>
+        <v>44978</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>14.7</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45068</v>
+        <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2591,14 +2591,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45791</v>
+        <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45545</v>
+        <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45631</v>
+        <v>45068</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45554</v>
+        <v>45098</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44596</v>
+        <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45547</v>
+        <v>45684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45658</v>
+        <v>45027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44816</v>
+        <v>45658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44977</v>
+        <v>45338</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45607</v>
+        <v>45314</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3401,7 +3401,7 @@
         <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45608</v>
+        <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45225</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44992</v>
+        <v>45628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45827</v>
+        <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45827</v>
+        <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45187</v>
+        <v>44992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45173</v>
+        <v>44783</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45314</v>
+        <v>45295</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4051,14 +4051,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45237</v>
+        <v>46084</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4070,8 +4070,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>45187</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45628</v>
+        <v>46023</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46058</v>
+        <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46058</v>
+        <v>44816</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4420,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44887</v>
+        <v>45322</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44951</v>
+        <v>45534</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4562,14 +4567,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45098</v>
+        <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4635,14 +4640,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46084</v>
+        <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4654,13 +4659,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45404</v>
+        <v>46210</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45616</v>
+        <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45546</v>
+        <v>44596</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45322</v>
+        <v>46252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44977</v>
+        <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45295</v>
+        <v>45621</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44784</v>
+        <v>45019</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45758</v>
+        <v>44784</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45545</v>
+        <v>46218</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44978</v>
+        <v>46223</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>46223</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45454</v>
+        <v>45554</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5535,13 +5535,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45684</v>
+        <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45684</v>
+        <v>44937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46023</v>
+        <v>45287</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5759,8 +5754,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46185</v>
+        <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46205</v>
+        <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46252</v>
+        <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>45698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6178,14 +6178,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46210</v>
+        <v>45791</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46218</v>
+        <v>45827</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>18.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46223</v>
+        <v>45827</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46223</v>
+        <v>45616</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.1</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45454</v>
+        <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1435,11 +1435,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>45698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45608</v>
+        <v>44951</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14.7</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45608</v>
+        <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45631</v>
+        <v>45534</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44887</v>
+        <v>44837</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44977</v>
+        <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45497</v>
+        <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45607</v>
+        <v>45554</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44837</v>
+        <v>45547</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2226,14 +2221,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44951</v>
+        <v>46084</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2245,8 +2240,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44978</v>
+        <v>45791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45546</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44978</v>
+        <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45173</v>
+        <v>45608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45545</v>
+        <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44951</v>
+        <v>45027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45068</v>
+        <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45098</v>
+        <v>45287</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,8 +2902,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45684</v>
+        <v>45621</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45684</v>
+        <v>45827</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>18.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45027</v>
+        <v>45827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45658</v>
+        <v>45497</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45338</v>
+        <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45314</v>
+        <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45628</v>
+        <v>44937</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45404</v>
+        <v>45338</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44977</v>
+        <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45628</v>
+        <v>46023</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46058</v>
+        <v>45608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>14.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46058</v>
+        <v>45068</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44992</v>
+        <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44783</v>
+        <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45295</v>
+        <v>45545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4051,14 +4056,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46084</v>
+        <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4070,13 +4075,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45187</v>
+        <v>45658</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46023</v>
+        <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46185</v>
+        <v>44816</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44816</v>
+        <v>45607</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45322</v>
+        <v>46252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45534</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45219</v>
+        <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46210</v>
+        <v>45225</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44596</v>
+        <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46252</v>
+        <v>45173</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45621</v>
+        <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45019</v>
+        <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44784</v>
+        <v>45237</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46218</v>
+        <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46223</v>
+        <v>45628</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46223</v>
+        <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45554</v>
+        <v>44951</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5589,14 +5589,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45545</v>
+        <v>45098</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44937</v>
+        <v>45404</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45287</v>
+        <v>45546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5754,13 +5754,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45225</v>
+        <v>45322</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45545</v>
+        <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45547</v>
+        <v>45295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45632</v>
+        <v>44784</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45698</v>
+        <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6178,14 +6173,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45791</v>
+        <v>44978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6193,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6236,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6250,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45827</v>
+        <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6266,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>18.7</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6309,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6323,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45827</v>
+        <v>45454</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6343,8 +6338,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45616</v>
+        <v>45632</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>44951</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45534</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>44837</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45554</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>45547</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46084</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45287</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45621</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>45827</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45497</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44937</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45338</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>46023</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45068</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45658</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44816</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45607</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45225</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45173</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45237</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45628</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44951</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45098</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45404</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45322</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44784</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45454</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45632</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>45698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>44951</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45534</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>44837</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45554</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>45547</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46084</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45287</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45621</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>45827</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45827</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45497</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45684</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44937</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45338</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>46023</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45608</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45068</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45545</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45658</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44816</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45607</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45225</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45173</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45237</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45628</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44951</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45098</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45404</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45546</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45322</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44977</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45295</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44784</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>45454</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45632</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45698</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44951</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44978</v>
+        <v>45698</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45534</v>
+        <v>45608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>14.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44837</v>
+        <v>45608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46058</v>
+        <v>45631</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1929,14 +1934,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46058</v>
+        <v>45791</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45554</v>
+        <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44596</v>
+        <v>44887</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45547</v>
+        <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>18.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2221,14 +2226,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46084</v>
+        <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2240,13 +2245,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45791</v>
+        <v>44977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45616</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45628</v>
+        <v>45497</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45608</v>
+        <v>45607</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44992</v>
+        <v>45237</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45027</v>
+        <v>46058</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45758</v>
+        <v>46058</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45219</v>
+        <v>44951</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45287</v>
+        <v>44978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,13 +2902,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45621</v>
+        <v>45546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3034,14 +3029,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45827</v>
+        <v>46084</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,8 +3048,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>18.7</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45827</v>
+        <v>44978</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45497</v>
+        <v>45173</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45684</v>
+        <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45684</v>
+        <v>44951</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44937</v>
+        <v>45068</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45338</v>
+        <v>45098</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45616</v>
+        <v>45027</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45608</v>
+        <v>45338</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45068</v>
+        <v>45314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46185</v>
+        <v>45628</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45545</v>
+        <v>45404</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45545</v>
+        <v>44977</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45631</v>
+        <v>45758</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45658</v>
+        <v>45684</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46205</v>
+        <v>45628</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44816</v>
+        <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45607</v>
+        <v>45684</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46252</v>
+        <v>44783</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46210</v>
+        <v>45295</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46210</v>
+        <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46210</v>
+        <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46218</v>
+        <v>46023</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45225</v>
+        <v>45322</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45187</v>
+        <v>45534</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45173</v>
+        <v>46185</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46223</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45314</v>
+        <v>44596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46223</v>
+        <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45237</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45631</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45628</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44887</v>
+        <v>46252</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44951</v>
+        <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5589,14 +5589,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45098</v>
+        <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45404</v>
+        <v>44784</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45546</v>
+        <v>45554</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45322</v>
+        <v>46218</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44977</v>
+        <v>46223</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45295</v>
+        <v>46223</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>6.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,8 +6192,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6236,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6250,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45019</v>
+        <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6266,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6309,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6323,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45454</v>
+        <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6338,13 +6343,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45632</v>
+        <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45454</v>
+        <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1435,11 +1435,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>45698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>44951</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45698</v>
+        <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45608</v>
+        <v>44837</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>14.7</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1788,14 +1783,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45608</v>
+        <v>45791</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45631</v>
+        <v>45534</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1934,14 +1929,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45791</v>
+        <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>18.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44837</v>
+        <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44887</v>
+        <v>45554</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45827</v>
+        <v>44596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>18.7</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45827</v>
+        <v>45547</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44977</v>
+        <v>45616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45616</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45497</v>
+        <v>46058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45607</v>
+        <v>46058</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45237</v>
+        <v>45628</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2606,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46058</v>
+        <v>45608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2679,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46058</v>
+        <v>44992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44951</v>
+        <v>45027</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2825,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2883,14 +2878,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44978</v>
+        <v>46084</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,8 +2897,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45546</v>
+        <v>45219</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46084</v>
+        <v>45287</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44978</v>
+        <v>45621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45173</v>
+        <v>45497</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44951</v>
+        <v>45338</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45068</v>
+        <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45098</v>
+        <v>45608</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>14.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45027</v>
+        <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45658</v>
+        <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45338</v>
+        <v>45545</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45314</v>
+        <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45628</v>
+        <v>45658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45404</v>
+        <v>45684</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44977</v>
+        <v>44816</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45758</v>
+        <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45684</v>
+        <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45628</v>
+        <v>45225</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44992</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45684</v>
+        <v>45173</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44783</v>
+        <v>46023</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45295</v>
+        <v>45314</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45187</v>
+        <v>45237</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44816</v>
+        <v>46185</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46023</v>
+        <v>45631</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45322</v>
+        <v>45628</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45534</v>
+        <v>46205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46185</v>
+        <v>44887</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>44951</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44596</v>
+        <v>45098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45621</v>
+        <v>46210</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46210</v>
+        <v>45404</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
         <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46252</v>
+        <v>45546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45019</v>
+        <v>45322</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44784</v>
+        <v>44977</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45554</v>
+        <v>46223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46223</v>
+        <v>45295</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46223</v>
+        <v>44784</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6034,7 +6034,7 @@
         <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44937</v>
+        <v>44978</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45287</v>
+        <v>45019</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,13 +6192,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6236,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6250,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45225</v>
+        <v>45454</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6270,8 +6265,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45545</v>
+        <v>45632</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45547</v>
+        <v>46252</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44723</v>
+        <v>44977</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44783</v>
+        <v>44723</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45698</v>
+        <v>44784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44951</v>
+        <v>45554</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44978</v>
+        <v>45628</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44837</v>
+        <v>44992</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45791</v>
+        <v>44783</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45534</v>
+        <v>45454</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1875,8 +1875,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45827</v>
+        <v>45295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45827</v>
+        <v>45545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45554</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44596</v>
+        <v>44937</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45547</v>
+        <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45616</v>
+        <v>45187</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45287</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2391,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46058</v>
+        <v>45225</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46058</v>
+        <v>44978</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45608</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44992</v>
+        <v>45546</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45027</v>
+        <v>44816</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2825,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2878,14 +2888,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46084</v>
+        <v>45547</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2897,13 +2907,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45219</v>
+        <v>45322</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45287</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3048,13 +3053,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45621</v>
+        <v>45534</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45497</v>
+        <v>45219</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44937</v>
+        <v>45632</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45338</v>
+        <v>45173</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45758</v>
+        <v>45608</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>14.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3479,7 +3479,7 @@
         <v>45608</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>14.7</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45068</v>
+        <v>45698</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45545</v>
+        <v>45631</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3698,7 +3698,7 @@
         <v>45545</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45631</v>
+        <v>44887</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45658</v>
+        <v>44951</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3910,14 +3910,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45684</v>
+        <v>45791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44816</v>
+        <v>44596</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45684</v>
+        <v>45621</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45607</v>
+        <v>45068</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45225</v>
+        <v>45098</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45173</v>
+        <v>44977</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46023</v>
+        <v>45827</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>18.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45314</v>
+        <v>45827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45237</v>
+        <v>45658</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46185</v>
+        <v>45338</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45631</v>
+        <v>45314</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45628</v>
+        <v>45019</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46205</v>
+        <v>45628</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44887</v>
+        <v>45616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44951</v>
+        <v>45404</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45098</v>
+        <v>45497</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46210</v>
+        <v>45607</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46210</v>
+        <v>44837</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45404</v>
+        <v>46058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>46058</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45546</v>
+        <v>46084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5462,8 +5462,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46218</v>
+        <v>45758</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>45684</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44977</v>
+        <v>45684</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5725,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46223</v>
+        <v>46023</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46223</v>
+        <v>46185</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45295</v>
+        <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44784</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45545</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44978</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45019</v>
+        <v>46218</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6193,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6236,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6250,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45454</v>
+        <v>46223</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6265,13 +6270,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45632</v>
+        <v>46223</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         <v>46252</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44977</v>
+        <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44723</v>
+        <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44784</v>
+        <v>45698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45554</v>
+        <v>44951</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45628</v>
+        <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44992</v>
+        <v>44837</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44783</v>
+        <v>46058</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45454</v>
+        <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1875,13 +1875,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45295</v>
+        <v>45534</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2007,14 +2002,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45545</v>
+        <v>46084</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2026,8 +2021,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45554</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44937</v>
+        <v>44596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44951</v>
+        <v>45547</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45187</v>
+        <v>45791</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45287</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2391,13 +2391,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45225</v>
+        <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44978</v>
+        <v>45608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45631</v>
+        <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>45027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45546</v>
+        <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44816</v>
+        <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>18.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45547</v>
+        <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45322</v>
+        <v>45219</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45534</v>
+        <v>45287</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3126,8 +3121,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45219</v>
+        <v>45621</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45632</v>
+        <v>45497</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45173</v>
+        <v>44937</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45608</v>
+        <v>45338</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45608</v>
+        <v>45684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45698</v>
+        <v>45684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45631</v>
+        <v>45608</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>14.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45545</v>
+        <v>45068</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>5.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44887</v>
+        <v>46023</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44951</v>
+        <v>45545</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3910,14 +3910,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45791</v>
+        <v>45545</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44596</v>
+        <v>45631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45621</v>
+        <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45068</v>
+        <v>45658</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45098</v>
+        <v>44816</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45027</v>
+        <v>45607</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44977</v>
+        <v>46205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45827</v>
+        <v>45225</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>18.7</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45827</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45658</v>
+        <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45338</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45314</v>
+        <v>45187</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45019</v>
+        <v>45173</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45628</v>
+        <v>45314</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45616</v>
+        <v>46218</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45404</v>
+        <v>45237</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45497</v>
+        <v>46223</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45607</v>
+        <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44837</v>
+        <v>45631</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46058</v>
+        <v>45628</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46058</v>
+        <v>44887</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46084</v>
+        <v>44951</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5462,13 +5462,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5521,14 +5516,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45758</v>
+        <v>45098</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45684</v>
+        <v>45404</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45684</v>
+        <v>45546</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46023</v>
+        <v>45322</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46185</v>
+        <v>44977</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46205</v>
+        <v>45295</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>44784</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46218</v>
+        <v>44978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6193,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6236,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6250,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46223</v>
+        <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6266,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6314,7 +6309,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6323,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46223</v>
+        <v>45454</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6343,8 +6338,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46252</v>
+        <v>45632</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1435,6 +1435,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45698</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44951</v>
+        <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44978</v>
+        <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44837</v>
+        <v>45632</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46058</v>
+        <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46058</v>
+        <v>44887</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45534</v>
+        <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2002,14 +2007,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46084</v>
+        <v>45698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2021,13 +2026,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2080,14 +2080,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45554</v>
+        <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44596</v>
+        <v>44977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45547</v>
+        <v>46058</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45791</v>
+        <v>46058</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45497</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45628</v>
+        <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2518,14 +2518,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45608</v>
+        <v>46084</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2537,8 +2537,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44992</v>
+        <v>45237</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45027</v>
+        <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45758</v>
+        <v>45827</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>18.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2817,7 +2822,7 @@
         <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>18.7</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45827</v>
+        <v>44978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45219</v>
+        <v>45546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45616</v>
+        <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45287</v>
+        <v>45616</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3121,13 +3126,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45621</v>
+        <v>45173</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45497</v>
+        <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44937</v>
+        <v>44951</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45338</v>
+        <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3479,7 +3479,7 @@
         <v>45684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45684</v>
+        <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45608</v>
+        <v>45098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>14.7</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45068</v>
+        <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46023</v>
+        <v>45027</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45545</v>
+        <v>45658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45545</v>
+        <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45631</v>
+        <v>45314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46185</v>
+        <v>45628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45658</v>
+        <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44816</v>
+        <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45607</v>
+        <v>46023</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46205</v>
+        <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45225</v>
+        <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46210</v>
+        <v>44992</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46210</v>
+        <v>44783</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46210</v>
+        <v>45295</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45187</v>
+        <v>46205</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45173</v>
+        <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45314</v>
+        <v>46210</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45237</v>
+        <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5158,7 +5158,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45631</v>
+        <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45628</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44887</v>
+        <v>45322</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44951</v>
+        <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5516,14 +5516,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45098</v>
+        <v>45219</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45404</v>
+        <v>44596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45546</v>
+        <v>45621</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45322</v>
+        <v>46252</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44977</v>
+        <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45295</v>
+        <v>44784</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46252</v>
+        <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,8 +6192,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6236,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6250,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45019</v>
+        <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6266,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6309,7 +6314,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6323,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45454</v>
+        <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6338,13 +6343,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45632</v>
+        <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45632</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44887</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>46058</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>46058</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45497</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>46084</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45237</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45827</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45616</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45173</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44951</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45027</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46023</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44992</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44783</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45295</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46205</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46210</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45322</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45219</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45621</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46252</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44784</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44476</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44723</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45608</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45632</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44887</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45698</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>44977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>46058</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>46058</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45497</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>46084</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45237</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45827</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>44978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>44978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45616</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45173</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44951</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45027</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44977</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>46023</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44992</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44783</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45295</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46205</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46210</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44816</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45322</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45219</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44596</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45621</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>46252</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44784</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45554</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44937</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45545</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE79"/>
+  <dimension ref="A1:AE78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 55146-2021</t>
+          <t>A 55757-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44474</v>
+        <v>44476</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55757-2021</t>
+          <t>A 55760-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 55760-2021</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44476</v>
+        <v>44784</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44784</v>
+        <v>44723</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44723</v>
+        <v>44783</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45454</v>
+        <v>44951</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,13 +1437,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>44978</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45608</v>
+        <v>45534</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14.7</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1642,14 +1637,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45608</v>
+        <v>45791</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45632</v>
+        <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>18.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45631</v>
+        <v>45827</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44887</v>
+        <v>45554</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44837</v>
+        <v>44596</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45698</v>
+        <v>45547</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2080,14 +2075,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45791</v>
+        <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44977</v>
+        <v>45616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46058</v>
+        <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2306,7 +2301,7 @@
         <v>46058</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45497</v>
+        <v>46058</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45607</v>
+        <v>45628</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2518,14 +2513,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46084</v>
+        <v>45608</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2537,13 +2532,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45237</v>
+        <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2606,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2669,14 +2659,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44951</v>
+        <v>46084</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2688,8 +2678,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45827</v>
+        <v>45027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>18.7</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45827</v>
+        <v>45219</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,8 +2902,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45546</v>
+        <v>45621</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44978</v>
+        <v>45497</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45616</v>
+        <v>44937</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45173</v>
+        <v>45338</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45545</v>
+        <v>45758</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44951</v>
+        <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45758</v>
+        <v>45068</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45684</v>
+        <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45068</v>
+        <v>45545</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45098</v>
+        <v>45684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3698,7 +3698,7 @@
         <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45027</v>
+        <v>45631</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>45658</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45338</v>
+        <v>44816</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45314</v>
+        <v>45607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45628</v>
+        <v>46023</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45404</v>
+        <v>45225</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44977</v>
+        <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46023</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46185</v>
+        <v>45173</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45628</v>
+        <v>45314</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44992</v>
+        <v>45237</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44783</v>
+        <v>46205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45295</v>
+        <v>45631</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46205</v>
+        <v>45628</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4866,7 +4866,7 @@
         <v>46210</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4939,7 +4939,7 @@
         <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>44887</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46218</v>
+        <v>44951</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44816</v>
+        <v>45098</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46223</v>
+        <v>45404</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45322</v>
+        <v>46223</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45534</v>
+        <v>46223</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45219</v>
+        <v>45546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44596</v>
+        <v>45322</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45621</v>
+        <v>44977</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46252</v>
+        <v>45295</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45019</v>
+        <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45554</v>
+        <v>44978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45545</v>
+        <v>45019</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44937</v>
+        <v>45454</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6119,8 +6119,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45287</v>
+        <v>46252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,13 +6197,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45225</v>
+        <v>45632</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6311,10 +6311,10 @@
       </c>
       <c r="V77" s="2" t="inlineStr"/>
     </row>
-    <row r="78" ht="15" customHeight="1">
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45545</v>
+        <v>45698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6383,79 +6383,6 @@
         <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>A 38871-2024</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>45547</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44476</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44476</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44784</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44723</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1362,6 +1362,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1408,7 +1413,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44951</v>
+        <v>45631</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44978</v>
+        <v>45608</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>14.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45534</v>
+        <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1637,14 +1642,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45791</v>
+        <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45827</v>
+        <v>44887</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>18.7</v>
+        <v>3.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45827</v>
+        <v>44977</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1856,14 +1861,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45554</v>
+        <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44596</v>
+        <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45547</v>
+        <v>46058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2082,7 +2087,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45616</v>
+        <v>45497</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44977</v>
+        <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46058</v>
+        <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>18.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2367,14 +2372,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46058</v>
+        <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2391,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45628</v>
+        <v>45827</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45608</v>
+        <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44992</v>
+        <v>45616</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2659,14 +2669,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46084</v>
+        <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2678,13 +2688,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45027</v>
+        <v>44978</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45219</v>
+        <v>45758</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45287</v>
+        <v>45546</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,13 +2907,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45621</v>
+        <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45497</v>
+        <v>45684</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44937</v>
+        <v>46023</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45338</v>
+        <v>44978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>0.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45758</v>
+        <v>46185</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45608</v>
+        <v>45173</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45068</v>
+        <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>0.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45545</v>
+        <v>44951</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45545</v>
+        <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>5.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45684</v>
+        <v>45098</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45684</v>
+        <v>46205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45631</v>
+        <v>46210</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45658</v>
+        <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44816</v>
+        <v>45027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45607</v>
+        <v>45658</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46023</v>
+        <v>45338</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45225</v>
+        <v>45314</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46185</v>
+        <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>45628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45173</v>
+        <v>45404</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45314</v>
+        <v>44977</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45237</v>
+        <v>46218</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45631</v>
+        <v>46223</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4720,7 +4720,7 @@
         <v>45628</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46210</v>
+        <v>44992</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46210</v>
+        <v>44783</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46210</v>
+        <v>45295</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44887</v>
+        <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44951</v>
+        <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46218</v>
+        <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45098</v>
+        <v>45534</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45404</v>
+        <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46223</v>
+        <v>46252</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46223</v>
+        <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45546</v>
+        <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44977</v>
+        <v>44784</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45295</v>
+        <v>45554</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5973,8 +5973,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45019</v>
+        <v>45225</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45454</v>
+        <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6119,13 +6124,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46252</v>
+        <v>45547</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>45632</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45698</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE78"/>
+  <dimension ref="A1:AE76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 55757-2021</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44476</v>
+        <v>45027</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 55760-2021</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44476</v>
+        <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44784</v>
+        <v>45219</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44723</v>
+        <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45454</v>
+        <v>44783</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1362,11 +1362,6 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1413,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45631</v>
+        <v>45287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1442,8 +1437,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45608</v>
+        <v>45621</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14.7</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45608</v>
+        <v>45454</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1588,8 +1588,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1637,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1651,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45631</v>
+        <v>45497</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1667,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1710,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1724,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44887</v>
+        <v>45632</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1740,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1783,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44977</v>
+        <v>44937</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1813,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1856,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1861,14 +1866,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45791</v>
+        <v>45698</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1886,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1929,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1943,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46058</v>
+        <v>45338</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1959,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +2002,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46058</v>
+        <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2032,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2075,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2080,14 +2085,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44837</v>
+        <v>45791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2105,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2148,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2162,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45497</v>
+        <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2178,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2221,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2235,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45607</v>
+        <v>44978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2251,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2306,7 +2311,7 @@
         <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2362,7 +2367,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2372,14 +2377,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46084</v>
+        <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2391,13 +2396,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45827</v>
+        <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>14.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45237</v>
+        <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45616</v>
+        <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44951</v>
+        <v>45545</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44978</v>
+        <v>45545</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45758</v>
+        <v>45631</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45546</v>
+        <v>45616</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45684</v>
+        <v>45554</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45684</v>
+        <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46023</v>
+        <v>45547</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44978</v>
+        <v>45658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46185</v>
+        <v>44816</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45173</v>
+        <v>45607</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45545</v>
+        <v>44977</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44951</v>
+        <v>45758</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45068</v>
+        <v>45684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45098</v>
+        <v>45628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46205</v>
+        <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46210</v>
+        <v>45608</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46210</v>
+        <v>45225</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45027</v>
+        <v>44992</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45658</v>
+        <v>45187</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45338</v>
+        <v>45173</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45314</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46210</v>
+        <v>45237</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45628</v>
+        <v>46023</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45404</v>
+        <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44977</v>
+        <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46223</v>
+        <v>46058</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46223</v>
+        <v>46058</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45628</v>
+        <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44992</v>
+        <v>44951</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44783</v>
+        <v>45098</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45295</v>
+        <v>45404</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5005,14 +5005,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>46084</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5024,8 +5024,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44816</v>
+        <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45322</v>
+        <v>45546</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5176,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45534</v>
+        <v>46210</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45219</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5322,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46252</v>
+        <v>45322</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44596</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45621</v>
+        <v>44977</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45019</v>
+        <v>46218</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44784</v>
+        <v>45295</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45554</v>
+        <v>46223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45545</v>
+        <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44937</v>
+        <v>46223</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45287</v>
+        <v>45545</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5973,13 +5978,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45225</v>
+        <v>44978</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45545</v>
+        <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
       </c>
       <c r="V75" s="2" t="inlineStr"/>
     </row>
-    <row r="76" ht="15" customHeight="1">
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45547</v>
+        <v>46252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6237,152 +6237,6 @@
         <v>0</v>
       </c>
       <c r="V76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>A 58657-2024</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>45632</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>A 6266-2025</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>45698</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45027</v>
+        <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45219</v>
+        <v>45454</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1218,8 +1218,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1267,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44784</v>
+        <v>45631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1297,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1340,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44783</v>
+        <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>14.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1413,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45287</v>
+        <v>45608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,13 +1442,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45621</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45454</v>
+        <v>44887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1588,13 +1588,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1637,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1651,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45497</v>
+        <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1667,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1710,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1724,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45632</v>
+        <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1740,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1783,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1797,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44937</v>
+        <v>45607</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1813,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1856,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1866,14 +1861,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45698</v>
+        <v>46084</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1885,8 +1880,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45338</v>
+        <v>45616</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45791</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2165,7 +2165,7 @@
         <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2238,7 +2238,7 @@
         <v>44978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2294,7 +2294,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45827</v>
+        <v>45546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>18.7</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45827</v>
+        <v>44978</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45608</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45068</v>
+        <v>45545</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.7</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45534</v>
+        <v>44951</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45545</v>
+        <v>45068</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>5.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2742,14 +2742,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45545</v>
+        <v>45098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45631</v>
+        <v>45027</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45616</v>
+        <v>45658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45554</v>
+        <v>45338</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44596</v>
+        <v>45314</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45547</v>
+        <v>45628</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45658</v>
+        <v>45404</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44816</v>
+        <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45607</v>
+        <v>46058</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44977</v>
+        <v>46058</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45758</v>
+        <v>45628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45684</v>
+        <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45628</v>
+        <v>44783</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45684</v>
+        <v>45758</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45608</v>
+        <v>45295</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45225</v>
+        <v>45684</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44992</v>
+        <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45187</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45173</v>
+        <v>44816</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45314</v>
+        <v>45322</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45237</v>
+        <v>45534</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46023</v>
+        <v>45219</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45631</v>
+        <v>46023</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45628</v>
+        <v>46185</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46185</v>
+        <v>44596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46058</v>
+        <v>45621</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46058</v>
+        <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44887</v>
+        <v>46210</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44951</v>
+        <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45098</v>
+        <v>45019</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45404</v>
+        <v>44784</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5005,14 +5005,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46084</v>
+        <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5024,13 +5024,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5087,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>45554</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45546</v>
+        <v>46218</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5176,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5219,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5249,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5292,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5306,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45322</v>
+        <v>45545</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44977</v>
+        <v>45287</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5540,8 +5535,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46218</v>
+        <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45295</v>
+        <v>45545</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46223</v>
+        <v>45547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44784</v>
+        <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46223</v>
+        <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5959,14 +5959,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45545</v>
+        <v>45791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44978</v>
+        <v>46252</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45019</v>
+        <v>45827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>18.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46252</v>
+        <v>45827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45454</v>
+        <v>44783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1216,11 +1216,6 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1267,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45631</v>
+        <v>44937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1297,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1340,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1354,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45608</v>
+        <v>45338</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1370,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1413,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45608</v>
+        <v>45295</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>44784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44887</v>
+        <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44977</v>
+        <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45497</v>
+        <v>44951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45607</v>
+        <v>44978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1861,14 +1856,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46084</v>
+        <v>45019</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1880,13 +1875,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1929,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1943,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45616</v>
+        <v>45454</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1958,8 +1948,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2019,7 +2014,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2075,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2089,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45534</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2105,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2148,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2162,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44951</v>
+        <v>45608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2178,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>14.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2221,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2235,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44978</v>
+        <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2251,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2294,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2367,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2381,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44978</v>
+        <v>45545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2397,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45545</v>
+        <v>45631</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44951</v>
+        <v>45554</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45068</v>
+        <v>44596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2742,14 +2737,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45098</v>
+        <v>45547</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45027</v>
+        <v>45698</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2895,7 +2890,7 @@
         <v>45658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45338</v>
+        <v>44816</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45314</v>
+        <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45628</v>
+        <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3180,14 +3175,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45404</v>
+        <v>45791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44977</v>
+        <v>45628</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46058</v>
+        <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46058</v>
+        <v>45827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>18.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45628</v>
+        <v>45827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3552,7 +3547,7 @@
         <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3608,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44783</v>
+        <v>45225</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45758</v>
+        <v>45187</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45295</v>
+        <v>45173</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45684</v>
+        <v>45616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45187</v>
+        <v>45314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45684</v>
+        <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44816</v>
+        <v>45027</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45322</v>
+        <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45534</v>
+        <v>45287</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4221,8 +4216,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45219</v>
+        <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46023</v>
+        <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46185</v>
+        <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44596</v>
+        <v>45497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45621</v>
+        <v>44887</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46205</v>
+        <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46210</v>
+        <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46210</v>
+        <v>45404</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45019</v>
+        <v>45546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44784</v>
+        <v>45758</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>45322</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45554</v>
+        <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46218</v>
+        <v>46058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46223</v>
+        <v>46058</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46223</v>
+        <v>45684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45545</v>
+        <v>45684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5443,14 +5443,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>46084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5462,8 +5462,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45287</v>
+        <v>46023</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5535,13 +5540,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45225</v>
+        <v>46185</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45545</v>
+        <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45547</v>
+        <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45632</v>
+        <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45698</v>
+        <v>46210</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5959,14 +5959,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45791</v>
+        <v>46218</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46252</v>
+        <v>46223</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45827</v>
+        <v>46223</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>18.7</v>
+        <v>6.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45827</v>
+        <v>46252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45338</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45295</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>44978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45019</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45454</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45534</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45631</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45554</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45547</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45698</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44816</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45628</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45225</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45187</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45173</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45027</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45287</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44887</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45404</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45758</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45322</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46058</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46023</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>46185</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>46210</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>46218</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>46223</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>46223</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>46252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44937</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45338</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45295</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44784</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>44978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>44978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45019</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>45454</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45534</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45608</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45545</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45631</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45554</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45547</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45698</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45658</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>44816</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45607</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45628</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45827</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45225</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45187</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45173</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45314</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>45027</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45287</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45621</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45631</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45628</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44887</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45404</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45758</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45322</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>46058</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46058</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>46084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46023</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>46185</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>46210</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>46218</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>46223</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>46223</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>46252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44783</v>
+        <v>44784</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44937</v>
+        <v>45554</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45338</v>
+        <v>44837</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45295</v>
+        <v>45545</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44784</v>
+        <v>46023</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44978</v>
+        <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44951</v>
+        <v>45287</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1727,6 +1727,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44978</v>
+        <v>45225</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45019</v>
+        <v>45545</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1936,7 +1941,7 @@
         <v>45454</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1997,7 +2002,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2016,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44837</v>
+        <v>45547</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2032,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2075,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2089,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45534</v>
+        <v>46205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2105,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2148,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2162,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45608</v>
+        <v>46210</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2178,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>14.7</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2221,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2235,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45068</v>
+        <v>46210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2251,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2294,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2308,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45545</v>
+        <v>46210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2324,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2367,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2381,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45545</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2397,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45632</v>
+        <v>45698</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45631</v>
+        <v>46218</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45554</v>
+        <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44596</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2737,14 +2742,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45547</v>
+        <v>45791</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45698</v>
+        <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>18.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45658</v>
+        <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44816</v>
+        <v>45631</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44977</v>
+        <v>45616</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45607</v>
+        <v>46058</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3175,14 +3180,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45791</v>
+        <v>46058</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45628</v>
+        <v>45608</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>14.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3328,7 +3333,7 @@
         <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3384,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45827</v>
+        <v>46252</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>18.7</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,14 +3472,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45827</v>
+        <v>46084</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3486,8 +3491,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44992</v>
+        <v>45631</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3570,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3613,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3627,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45225</v>
+        <v>44887</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3643,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3686,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3700,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45187</v>
+        <v>44977</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3749,7 +3759,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3773,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45173</v>
+        <v>45497</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3789,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3832,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3836,10 +3846,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45616</v>
+        <v>45607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3852,7 +3862,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3905,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3919,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45314</v>
+        <v>45758</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3925,7 +3935,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3978,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3982,10 +3992,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45237</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3998,7 +4008,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4051,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4055,10 +4065,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45027</v>
+        <v>45684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4071,7 +4081,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4114,7 +4124,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4128,10 +4138,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45219</v>
+        <v>45237</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4144,7 +4154,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4187,7 +4197,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4201,10 +4211,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45287</v>
+        <v>44951</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4216,13 +4226,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4270,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4284,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45621</v>
+        <v>44978</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4338,7 +4343,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4357,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45631</v>
+        <v>45546</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4373,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4416,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4430,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45628</v>
+        <v>44978</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4446,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4489,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4503,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45497</v>
+        <v>45173</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4519,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4562,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4576,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44887</v>
+        <v>45545</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4592,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4635,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4647,7 +4652,7 @@
         <v>44951</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4665,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4708,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4713,14 +4718,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45098</v>
+        <v>45068</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4738,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4781,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4786,14 +4791,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45404</v>
+        <v>45098</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4811,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45546</v>
+        <v>45027</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4884,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4927,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4941,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45758</v>
+        <v>45658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4995,7 +5000,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5014,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45322</v>
+        <v>45338</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5030,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44977</v>
+        <v>45314</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46058</v>
+        <v>45628</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5176,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46058</v>
+        <v>45404</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45684</v>
+        <v>44977</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5360,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45684</v>
+        <v>45628</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5443,14 +5448,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46084</v>
+        <v>44992</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5462,13 +5467,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46023</v>
+        <v>44783</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46185</v>
+        <v>45295</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46205</v>
+        <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46210</v>
+        <v>44816</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46210</v>
+        <v>45322</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46210</v>
+        <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46218</v>
+        <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46223</v>
+        <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46223</v>
+        <v>45621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46252</v>
+        <v>45019</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44784</v>
+        <v>44783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45554</v>
+        <v>45698</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44837</v>
+        <v>44951</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45545</v>
+        <v>44978</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46023</v>
+        <v>45791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44937</v>
+        <v>44837</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46185</v>
+        <v>45534</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45287</v>
+        <v>45827</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1729,13 +1729,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>18.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45225</v>
+        <v>45827</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45545</v>
+        <v>45616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45454</v>
+        <v>45554</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1953,13 +1948,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2002,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2016,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45547</v>
+        <v>44596</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2032,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2075,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2089,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46205</v>
+        <v>45547</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2105,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2148,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2162,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46210</v>
+        <v>44977</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2178,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2221,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2235,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46210</v>
+        <v>46058</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2251,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2294,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2308,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46210</v>
+        <v>46058</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2324,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2367,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2381,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2397,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45698</v>
+        <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46218</v>
+        <v>44992</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2596,14 +2586,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46223</v>
+        <v>46084</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2615,8 +2605,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46223</v>
+        <v>45027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2742,14 +2737,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45791</v>
+        <v>45219</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45827</v>
+        <v>45287</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,8 +2829,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>18.7</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45827</v>
+        <v>45621</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45631</v>
+        <v>45497</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45616</v>
+        <v>44937</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46058</v>
+        <v>45338</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46058</v>
+        <v>45758</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>45608</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45608</v>
+        <v>45068</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46252</v>
+        <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46084</v>
+        <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3491,13 +3491,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3557,7 +3552,7 @@
         <v>45631</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3613,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3627,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44887</v>
+        <v>45684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3643,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3686,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3700,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44977</v>
+        <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3716,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3759,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3773,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45497</v>
+        <v>45658</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3832,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3846,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45607</v>
+        <v>44816</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3862,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3905,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3919,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45758</v>
+        <v>45607</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3935,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3978,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3992,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45684</v>
+        <v>46023</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4008,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4051,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4065,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45684</v>
+        <v>45225</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4081,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4124,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4138,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45237</v>
+        <v>45187</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4154,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4197,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4211,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44951</v>
+        <v>45173</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4227,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4270,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4284,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44978</v>
+        <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4300,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4343,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4357,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45546</v>
+        <v>45314</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4373,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4416,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44978</v>
+        <v>45237</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4446,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4489,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45173</v>
+        <v>45631</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4519,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45545</v>
+        <v>45628</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4592,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44951</v>
+        <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4665,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4708,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4722,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45068</v>
+        <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4738,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4781,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4791,14 +4786,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45098</v>
+        <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4811,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4854,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45027</v>
+        <v>44951</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4884,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4927,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4941,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45658</v>
+        <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4957,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5000,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5014,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45338</v>
+        <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5030,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5083,14 +5078,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45314</v>
+        <v>45098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45628</v>
+        <v>46218</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5176,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5236,7 +5231,7 @@
         <v>45404</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5292,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5306,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44977</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45628</v>
+        <v>46223</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44992</v>
+        <v>45546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44783</v>
+        <v>45322</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45295</v>
+        <v>44977</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45187</v>
+        <v>45295</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44816</v>
+        <v>44784</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45322</v>
+        <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45534</v>
+        <v>44978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5949,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45219</v>
+        <v>45019</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44596</v>
+        <v>45454</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6051,8 +6046,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45621</v>
+        <v>46252</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45019</v>
+        <v>45632</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44784</v>
+        <v>45698</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44783</v>
+        <v>44784</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45698</v>
+        <v>45173</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1345,14 +1345,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44951</v>
+        <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44978</v>
+        <v>45454</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,8 +1437,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1491,14 +1496,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45791</v>
+        <v>45827</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>18.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44837</v>
+        <v>45827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45534</v>
+        <v>45545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45827</v>
+        <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>18.7</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45827</v>
+        <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45616</v>
+        <v>44837</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45554</v>
+        <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44596</v>
+        <v>45608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>14.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45547</v>
+        <v>45608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44977</v>
+        <v>45631</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46058</v>
+        <v>44887</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46058</v>
+        <v>44977</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2367,14 +2372,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45628</v>
+        <v>46084</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2391,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45608</v>
+        <v>45068</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2513,14 +2523,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44992</v>
+        <v>45098</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2586,14 +2596,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46084</v>
+        <v>45497</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2605,13 +2615,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45027</v>
+        <v>45607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45219</v>
+        <v>45027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45287</v>
+        <v>45658</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2829,13 +2834,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45621</v>
+        <v>45338</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45497</v>
+        <v>45314</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44937</v>
+        <v>45237</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45338</v>
+        <v>44951</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45758</v>
+        <v>44978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45608</v>
+        <v>45546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>14.7</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45068</v>
+        <v>44978</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.7</v>
+        <v>0.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45545</v>
+        <v>46058</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45545</v>
+        <v>46058</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45631</v>
+        <v>45758</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45684</v>
+        <v>45628</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
         <v>45684</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45658</v>
+        <v>45684</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44816</v>
+        <v>45404</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45607</v>
+        <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46023</v>
+        <v>45628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45225</v>
+        <v>44992</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45187</v>
+        <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45173</v>
+        <v>45295</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46185</v>
+        <v>46023</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45314</v>
+        <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45237</v>
+        <v>45187</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45631</v>
+        <v>44816</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45628</v>
+        <v>46205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44887</v>
+        <v>46210</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46210</v>
+        <v>45322</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44951</v>
+        <v>46210</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46210</v>
+        <v>45534</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>45219</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45098</v>
+        <v>46218</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45404</v>
+        <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46223</v>
+        <v>44596</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46223</v>
+        <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45546</v>
+        <v>45019</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45322</v>
+        <v>44784</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44977</v>
+        <v>45554</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45295</v>
+        <v>46252</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5900,8 +5900,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45019</v>
+        <v>45225</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45454</v>
+        <v>45545</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6046,13 +6051,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46252</v>
+        <v>45547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6185,7 +6185,7 @@
         <v>45632</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45698</v>
+        <v>45621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>44784</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45173</v>
+        <v>44783</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>45791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45454</v>
+        <v>45497</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1437,13 +1437,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1503,7 +1498,7 @@
         <v>45827</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1571,7 @@
         <v>45827</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45545</v>
+        <v>44937</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45631</v>
+        <v>45338</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1795,7 +1790,7 @@
         <v>45616</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44837</v>
+        <v>44951</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44951</v>
+        <v>44978</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45608</v>
+        <v>45534</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>14.7</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2087,7 +2082,7 @@
         <v>45608</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>14.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45631</v>
+        <v>45068</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44887</v>
+        <v>45545</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44977</v>
+        <v>45545</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2362,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2372,14 +2367,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46084</v>
+        <v>45554</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2391,13 +2386,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45068</v>
+        <v>44596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2523,14 +2513,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45098</v>
+        <v>45547</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45497</v>
+        <v>45631</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2606,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45607</v>
+        <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2679,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45027</v>
+        <v>45658</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45658</v>
+        <v>44816</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2825,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2882,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45338</v>
+        <v>45607</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2898,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2941,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2955,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45314</v>
+        <v>44837</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2971,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3014,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3028,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45237</v>
+        <v>45628</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3044,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3087,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3101,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44951</v>
+        <v>45758</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3117,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3160,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3174,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44978</v>
+        <v>45608</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3190,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3233,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3247,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45546</v>
+        <v>44992</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3263,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3306,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3320,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44978</v>
+        <v>45225</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3336,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3379,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3393,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46058</v>
+        <v>45187</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3409,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3452,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3466,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46058</v>
+        <v>45173</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3482,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3525,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3539,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45758</v>
+        <v>45027</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3555,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3598,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3612,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45628</v>
+        <v>45684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3628,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3671,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3685,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45684</v>
+        <v>45314</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3701,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3744,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3758,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45684</v>
+        <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3774,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3817,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3831,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45404</v>
+        <v>45684</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3847,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3890,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3904,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44977</v>
+        <v>45287</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3929,8 +3919,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45628</v>
+        <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44992</v>
+        <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44783</v>
+        <v>45628</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45295</v>
+        <v>46023</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46023</v>
+        <v>44887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46185</v>
+        <v>44951</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4421,14 +4416,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45187</v>
+        <v>45098</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4436,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4479,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44816</v>
+        <v>46185</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4509,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4552,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4566,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46205</v>
+        <v>45404</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4582,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4625,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46210</v>
+        <v>45546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4655,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4698,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4793,7 +4788,7 @@
         <v>45322</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4849,7 +4844,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46210</v>
+        <v>44977</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4874,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4917,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45534</v>
+        <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4947,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4990,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45219</v>
+        <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5063,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5077,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5093,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5136,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5166,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5209,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5231,7 +5226,7 @@
         <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5239,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5282,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5296,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44596</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5312,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5355,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45621</v>
+        <v>45295</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5385,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5428,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5442,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45019</v>
+        <v>44784</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5458,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5501,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5515,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44784</v>
+        <v>45545</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5531,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5574,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5588,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45554</v>
+        <v>44978</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5604,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5647,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46252</v>
+        <v>45019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5677,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5720,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5734,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45545</v>
+        <v>45454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5754,8 +5749,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44937</v>
+        <v>46252</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45287</v>
+        <v>45632</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5900,13 +5900,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45225</v>
+        <v>45698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5974,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45545</v>
+        <v>46058</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45547</v>
+        <v>46058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6163,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6178,14 +6173,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45632</v>
+        <v>46084</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6197,8 +6192,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45621</v>
+        <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44784</v>
+        <v>45454</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1218,8 +1218,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1267,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44783</v>
+        <v>45631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1297,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1340,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1345,14 +1350,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45791</v>
+        <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>14.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1413,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45497</v>
+        <v>45608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45827</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>18.7</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45827</v>
+        <v>44887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44937</v>
+        <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45338</v>
+        <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45616</v>
+        <v>45607</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44951</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44978</v>
+        <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45534</v>
+        <v>44978</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45608</v>
+        <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14.7</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45068</v>
+        <v>45758</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45545</v>
+        <v>44978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45554</v>
+        <v>45684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44596</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45547</v>
+        <v>45684</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45631</v>
+        <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44977</v>
+        <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45658</v>
+        <v>45068</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2805,14 +2810,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44816</v>
+        <v>45098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2825,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45607</v>
+        <v>45027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2898,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2941,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2955,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44837</v>
+        <v>45658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2971,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3014,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3028,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45628</v>
+        <v>45338</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3044,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3087,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3101,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45758</v>
+        <v>45314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3117,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3160,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3174,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45608</v>
+        <v>45628</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3190,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3233,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3247,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44992</v>
+        <v>45404</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3263,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3306,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3320,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45225</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3336,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3379,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3393,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45187</v>
+        <v>46023</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3409,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3452,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3466,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45173</v>
+        <v>45628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3482,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3525,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3539,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45027</v>
+        <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3555,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3598,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3612,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45684</v>
+        <v>44783</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3628,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3671,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3685,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45314</v>
+        <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3701,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3744,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3758,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45219</v>
+        <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3774,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3817,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3831,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45684</v>
+        <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3847,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3890,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3904,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45287</v>
+        <v>45295</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3919,13 +3924,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3978,14 +3978,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45237</v>
+        <v>46084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3997,8 +3997,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45631</v>
+        <v>45187</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45628</v>
+        <v>44816</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46023</v>
+        <v>45322</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44887</v>
+        <v>45534</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44951</v>
+        <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4416,14 +4421,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45098</v>
+        <v>46205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4436,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4479,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46185</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4552,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4566,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45404</v>
+        <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4582,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4625,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45546</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4655,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4698,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4728,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4771,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4785,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45322</v>
+        <v>46223</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4844,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44977</v>
+        <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4874,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4917,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46210</v>
+        <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4947,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4990,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5004,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5020,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5063,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5077,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46210</v>
+        <v>45019</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5093,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5136,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5150,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46218</v>
+        <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5166,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5209,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5223,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46223</v>
+        <v>45554</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5239,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5282,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5296,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46223</v>
+        <v>45545</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5312,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5355,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45295</v>
+        <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5385,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5428,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5442,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44784</v>
+        <v>45287</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5457,8 +5462,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5501,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5515,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45545</v>
+        <v>46252</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5531,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5574,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5588,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44978</v>
+        <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5604,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5647,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5661,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45019</v>
+        <v>45545</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5677,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5720,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5734,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45454</v>
+        <v>45547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5749,13 +5759,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46252</v>
+        <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45632</v>
+        <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5954,14 +5959,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45698</v>
+        <v>45791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46058</v>
+        <v>45827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.5</v>
+        <v>18.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46058</v>
+        <v>45827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6173,14 +6178,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46084</v>
+        <v>45616</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,13 +6197,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45454</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>45631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45607</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>44978</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45758</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45684</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45068</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45338</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45628</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45404</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46023</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44783</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45295</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45187</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44816</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45322</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45534</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46223</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45019</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45554</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45545</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45287</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46252</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45545</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45616</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45454</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>45631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>45608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45497</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>45607</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>44978</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45758</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>44978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45684</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44951</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45068</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45658</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45338</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45314</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45628</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45404</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46023</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44783</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45295</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46084</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45187</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44816</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45322</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45534</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>46205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>46223</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45019</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>44784</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45554</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45545</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45287</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46252</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45545</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45547</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45616</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45454</v>
+        <v>44783</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1216,11 +1216,6 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>KUMLA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1267,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45631</v>
+        <v>44951</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1297,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1340,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1354,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45608</v>
+        <v>44978</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1370,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>14.7</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1413,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45608</v>
+        <v>45534</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45631</v>
+        <v>45554</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44887</v>
+        <v>45547</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44977</v>
+        <v>44596</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45497</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45607</v>
+        <v>45628</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44951</v>
+        <v>44992</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44978</v>
+        <v>45758</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44837</v>
+        <v>45027</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45758</v>
+        <v>44837</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45546</v>
+        <v>45219</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44978</v>
+        <v>45287</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2318,8 +2313,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45684</v>
+        <v>45621</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>45497</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45684</v>
+        <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45545</v>
+        <v>45338</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44951</v>
+        <v>45684</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45068</v>
+        <v>45684</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2810,14 +2810,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45098</v>
+        <v>45608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>14.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45027</v>
+        <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45658</v>
+        <v>45545</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45338</v>
+        <v>45545</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45314</v>
+        <v>45631</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45628</v>
+        <v>45658</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45404</v>
+        <v>44816</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44977</v>
+        <v>46023</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46023</v>
+        <v>45607</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45628</v>
+        <v>46058</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44992</v>
+        <v>46058</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44783</v>
+        <v>46185</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46058</v>
+        <v>45225</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46058</v>
+        <v>45187</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3832,14 +3832,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46185</v>
+        <v>46084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3851,8 +3851,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45295</v>
+        <v>45173</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3978,14 +3983,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46084</v>
+        <v>45314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3997,13 +4002,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45187</v>
+        <v>45237</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44816</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45322</v>
+        <v>45628</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45534</v>
+        <v>46205</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45219</v>
+        <v>44887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46205</v>
+        <v>44951</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46210</v>
+        <v>45098</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4574,7 +4574,7 @@
         <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46223</v>
+        <v>45404</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46223</v>
+        <v>45546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44596</v>
+        <v>46218</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45621</v>
+        <v>46223</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45019</v>
+        <v>46223</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44784</v>
+        <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45554</v>
+        <v>44977</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45545</v>
+        <v>45295</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44937</v>
+        <v>44784</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45287</v>
+        <v>45545</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5462,13 +5462,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46252</v>
+        <v>44978</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45225</v>
+        <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45545</v>
+        <v>46252</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45547</v>
+        <v>45454</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5759,8 +5754,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5820,7 +5820,7 @@
         <v>45632</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45827</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45616</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1216,6 +1216,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1262,7 +1267,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44951</v>
+        <v>45631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1297,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1340,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44978</v>
+        <v>45632</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1413,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45534</v>
+        <v>45698</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45554</v>
+        <v>45608</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>14.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45547</v>
+        <v>45608</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1637,14 +1642,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44596</v>
+        <v>45791</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44977</v>
+        <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45628</v>
+        <v>44887</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1865,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45608</v>
+        <v>44837</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44992</v>
+        <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45758</v>
+        <v>44977</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45027</v>
+        <v>46058</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44837</v>
+        <v>45497</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45219</v>
+        <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2294,14 +2299,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45287</v>
+        <v>46084</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2324,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2367,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2381,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45621</v>
+        <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2397,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>18.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45497</v>
+        <v>45827</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44937</v>
+        <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45338</v>
+        <v>44951</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45684</v>
+        <v>45616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45684</v>
+        <v>44978</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45608</v>
+        <v>45546</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>14.7</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45068</v>
+        <v>44978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.7</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45545</v>
+        <v>45758</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45545</v>
+        <v>45173</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45631</v>
+        <v>45684</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45658</v>
+        <v>45545</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44816</v>
+        <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46023</v>
+        <v>44951</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45607</v>
+        <v>45068</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,14 +3472,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46058</v>
+        <v>45098</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46058</v>
+        <v>45027</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46185</v>
+        <v>45658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45225</v>
+        <v>45338</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45187</v>
+        <v>45314</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3832,14 +3837,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46084</v>
+        <v>46023</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3851,13 +3856,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45173</v>
+        <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45314</v>
+        <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45237</v>
+        <v>45404</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>44977</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4209,7 +4209,7 @@
         <v>45628</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46205</v>
+        <v>44992</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44887</v>
+        <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44951</v>
+        <v>46205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45098</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4574,7 +4574,7 @@
         <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46210</v>
+        <v>45295</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45404</v>
+        <v>46218</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45546</v>
+        <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46223</v>
+        <v>45187</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46223</v>
+        <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44977</v>
+        <v>45534</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45295</v>
+        <v>45219</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44784</v>
+        <v>46252</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45545</v>
+        <v>44596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.1</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44978</v>
+        <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>45019</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46252</v>
+        <v>44784</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45454</v>
+        <v>45554</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5754,13 +5754,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45632</v>
+        <v>45545</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45698</v>
+        <v>44937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5959,14 +5954,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45791</v>
+        <v>45287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5978,8 +5973,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45827</v>
+        <v>45225</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>18.7</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45827</v>
+        <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45616</v>
+        <v>45547</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44723</v>
+        <v>44783</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45454</v>
+        <v>44723</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1218,13 +1218,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1267,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1297,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1340,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1354,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45632</v>
+        <v>45698</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1370,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1413,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45698</v>
+        <v>44951</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1500,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45608</v>
+        <v>44978</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14.7</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1569,14 +1564,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45608</v>
+        <v>45791</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1642,14 +1637,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45791</v>
+        <v>44837</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45631</v>
+        <v>45534</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44887</v>
+        <v>45827</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>18.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44837</v>
+        <v>45827</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46058</v>
+        <v>45554</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44977</v>
+        <v>45616</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46058</v>
+        <v>44596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45497</v>
+        <v>45547</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45607</v>
+        <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2299,14 +2294,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46084</v>
+        <v>45628</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2318,13 +2313,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2367,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2381,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45827</v>
+        <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2397,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>18.7</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45827</v>
+        <v>44992</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>0.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45237</v>
+        <v>46058</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44951</v>
+        <v>46058</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2606,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45616</v>
+        <v>45027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2679,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44978</v>
+        <v>45219</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45546</v>
+        <v>45287</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,8 +2824,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44978</v>
+        <v>45621</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2961,14 +2956,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45758</v>
+        <v>46084</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2980,8 +2975,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45173</v>
+        <v>45497</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45684</v>
+        <v>44937</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45545</v>
+        <v>45338</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45684</v>
+        <v>45758</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44951</v>
+        <v>45608</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>45068</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45098</v>
+        <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45027</v>
+        <v>45545</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45658</v>
+        <v>45631</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45338</v>
+        <v>45658</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45314</v>
+        <v>44816</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46023</v>
+        <v>45607</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45628</v>
+        <v>45684</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46185</v>
+        <v>45684</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45404</v>
+        <v>45225</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44977</v>
+        <v>45187</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45628</v>
+        <v>45173</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44992</v>
+        <v>46023</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44783</v>
+        <v>45314</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46205</v>
+        <v>45237</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46210</v>
+        <v>46185</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46210</v>
+        <v>45631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46210</v>
+        <v>45628</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45295</v>
+        <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46223</v>
+        <v>44951</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46223</v>
+        <v>45098</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45187</v>
+        <v>46210</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44816</v>
+        <v>45404</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45322</v>
+        <v>46210</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45534</v>
+        <v>46210</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45219</v>
+        <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46252</v>
+        <v>46218</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44596</v>
+        <v>46223</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45621</v>
+        <v>46223</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45019</v>
+        <v>45322</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44784</v>
+        <v>44977</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45554</v>
+        <v>45295</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45545</v>
+        <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44937</v>
+        <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45287</v>
+        <v>44978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5973,13 +5973,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6017,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6031,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45225</v>
+        <v>45019</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6047,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6090,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45545</v>
+        <v>46252</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6120,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6163,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45547</v>
+        <v>45454</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6197,8 +6192,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44783</v>
+        <v>45454</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,6 +1143,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>KUMLA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1206,7 +1211,7 @@
         <v>44723</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1262,7 +1267,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1297,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1340,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45698</v>
+        <v>44992</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1413,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44951</v>
+        <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1491,14 +1496,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44978</v>
+        <v>45791</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1564,14 +1569,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45791</v>
+        <v>45295</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44837</v>
+        <v>45187</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45534</v>
+        <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1790,7 +1795,7 @@
         <v>45827</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1868,7 @@
         <v>45827</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45554</v>
+        <v>44816</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2009,7 +2014,7 @@
         <v>45616</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2065,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44596</v>
+        <v>45322</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45547</v>
+        <v>44837</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44977</v>
+        <v>45534</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2284,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45628</v>
+        <v>45219</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2374,7 +2379,7 @@
         <v>45608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>14.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44992</v>
+        <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46058</v>
+        <v>44596</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46058</v>
+        <v>45621</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45027</v>
+        <v>45631</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45219</v>
+        <v>45758</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45287</v>
+        <v>45019</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2824,13 +2829,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45621</v>
+        <v>44784</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2956,14 +2956,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46084</v>
+        <v>45684</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2975,13 +2975,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45497</v>
+        <v>44887</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44937</v>
+        <v>45554</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45338</v>
+        <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45758</v>
+        <v>45545</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45608</v>
+        <v>44937</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>14.7</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45068</v>
+        <v>45287</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3418,8 +3413,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45545</v>
+        <v>45225</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3552,7 +3552,7 @@
         <v>45545</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45631</v>
+        <v>45547</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44816</v>
+        <v>46058</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45607</v>
+        <v>46058</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45684</v>
+        <v>44977</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45684</v>
+        <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45225</v>
+        <v>45632</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45187</v>
+        <v>45698</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45173</v>
+        <v>46084</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4221,8 +4221,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4270,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4284,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46023</v>
+        <v>45497</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4300,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4343,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4357,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45314</v>
+        <v>46205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4373,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4416,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4425,10 +4430,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45237</v>
+        <v>46210</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4446,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4489,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4503,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46185</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4514,7 +4519,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4562,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4576,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45631</v>
+        <v>45607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4592,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4635,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45628</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4660,7 +4665,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4703,7 +4708,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4717,10 +4722,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44887</v>
+        <v>46218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4733,7 +4738,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4776,7 +4781,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4790,10 +4795,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4806,7 +4811,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4849,7 +4854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4863,10 +4868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44951</v>
+        <v>46223</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4879,7 +4884,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4922,7 +4927,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4932,14 +4937,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45098</v>
+        <v>45237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4952,7 +4957,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4995,7 +5000,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5009,10 +5014,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46210</v>
+        <v>44951</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5025,7 +5030,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5068,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5082,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45404</v>
+        <v>44978</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5098,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5141,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5155,10 +5160,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46210</v>
+        <v>45546</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5171,7 +5176,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>0.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5214,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5244,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5287,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45546</v>
+        <v>44978</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5317,7 +5322,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5360,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5374,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46218</v>
+        <v>45173</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5390,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5433,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5447,10 +5452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46223</v>
+        <v>45545</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5463,7 +5468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5506,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5520,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46223</v>
+        <v>44951</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5536,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5579,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5593,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45322</v>
+        <v>45068</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5609,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5652,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5662,14 +5667,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44977</v>
+        <v>45098</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5682,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5725,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45295</v>
+        <v>45027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5755,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5798,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44784</v>
+        <v>45658</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5828,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5871,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5885,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45545</v>
+        <v>45338</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5901,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5944,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5958,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44978</v>
+        <v>45314</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5974,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6017,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45019</v>
+        <v>45628</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6047,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6090,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46252</v>
+        <v>45404</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6120,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6163,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45454</v>
+        <v>44977</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6192,13 +6197,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45454</v>
+        <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1145,13 +1145,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1194,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1204,14 +1199,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44723</v>
+        <v>45098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1224,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1267,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1281,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45628</v>
+        <v>44783</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1297,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1340,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1354,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44992</v>
+        <v>45404</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1370,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1413,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44783</v>
+        <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1486,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1496,14 +1491,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45791</v>
+        <v>44837</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1516,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45295</v>
+        <v>45322</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45187</v>
+        <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45631</v>
+        <v>46023</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45827</v>
+        <v>45295</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1851,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45827</v>
+        <v>46185</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1938,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44816</v>
+        <v>44784</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1954,7 +1949,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45616</v>
+        <v>45545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2027,7 +2022,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2065,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45322</v>
+        <v>44978</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2095,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44837</v>
+        <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45534</v>
+        <v>46210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45219</v>
+        <v>45019</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45608</v>
+        <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>14.7</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45608</v>
+        <v>46210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2508,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44596</v>
+        <v>45454</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2537,8 +2532,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45621</v>
+        <v>46218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45631</v>
+        <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45758</v>
+        <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45019</v>
+        <v>45632</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44784</v>
+        <v>45698</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45684</v>
+        <v>46058</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44887</v>
+        <v>46058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3102,14 +3102,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45554</v>
+        <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45684</v>
+        <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45545</v>
+        <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>18.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44937</v>
+        <v>45827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45287</v>
+        <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45225</v>
+        <v>44951</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45545</v>
+        <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45547</v>
+        <v>44978</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46023</v>
+        <v>45534</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46058</v>
+        <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46058</v>
+        <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44977</v>
+        <v>44596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46185</v>
+        <v>45547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45632</v>
+        <v>44977</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45698</v>
+        <v>45684</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46084</v>
+        <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4221,13 +4221,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4270,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4284,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45497</v>
+        <v>45628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4300,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4343,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4357,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46205</v>
+        <v>45608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4373,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4416,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46210</v>
+        <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4446,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4489,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46210</v>
+        <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4519,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45607</v>
+        <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4592,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46210</v>
+        <v>45287</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4664,8 +4659,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46218</v>
+        <v>45621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46223</v>
+        <v>45497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46223</v>
+        <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45237</v>
+        <v>45338</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44951</v>
+        <v>45608</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>14.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44978</v>
+        <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2</v>
+        <v>5.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46252</v>
+        <v>45545</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44978</v>
+        <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45173</v>
+        <v>45658</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45545</v>
+        <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44951</v>
+        <v>45607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45068</v>
+        <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5667,14 +5667,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45098</v>
+        <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45027</v>
+        <v>45173</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45658</v>
+        <v>45314</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45338</v>
+        <v>45237</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45314</v>
+        <v>45631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45628</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45404</v>
+        <v>44887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44977</v>
+        <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44783</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45404</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44837</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>45322</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>46023</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45295</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46185</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44784</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44978</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45019</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45454</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45632</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45698</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>46058</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>46058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44951</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44978</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45534</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>44596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44977</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45684</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45287</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>45338</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45608</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>45545</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45658</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45173</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45314</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45237</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45628</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45098</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44783</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45404</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>45546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44837</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>45322</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>44977</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>46023</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>45295</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46185</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44784</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45545</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44978</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45019</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45454</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45632</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45698</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>46058</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>46058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46252</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46084</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>44951</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44978</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45534</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>44596</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44977</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45684</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44992</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>45219</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45287</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>45338</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45608</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45068</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>45545</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45658</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45173</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45314</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>45237</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45628</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1199,14 +1199,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45098</v>
+        <v>44784</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44783</v>
+        <v>46185</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45404</v>
+        <v>45554</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45546</v>
+        <v>44837</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44837</v>
+        <v>45454</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1510,8 +1510,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45322</v>
+        <v>45545</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44977</v>
+        <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46023</v>
+        <v>44937</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45295</v>
+        <v>45287</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1802,8 +1807,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1856,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1860,10 +1870,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46185</v>
+        <v>45608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1886,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>14.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1929,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1943,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44784</v>
+        <v>45225</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1959,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +2002,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2016,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45545</v>
+        <v>45608</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,7 +2032,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2065,7 +2075,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2079,10 +2089,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44978</v>
+        <v>45545</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2138,7 +2148,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2162,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46205</v>
+        <v>45547</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2178,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2221,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2235,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46210</v>
+        <v>45631</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2251,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2294,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2308,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45019</v>
+        <v>44887</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2324,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2367,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2381,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46210</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2397,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46210</v>
+        <v>44977</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45454</v>
+        <v>45698</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2532,13 +2542,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2591,14 +2596,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46218</v>
+        <v>45791</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46223</v>
+        <v>45497</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46223</v>
+        <v>45607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45632</v>
+        <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>18.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45698</v>
+        <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46058</v>
+        <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46058</v>
+        <v>45237</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3102,14 +3107,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45791</v>
+        <v>44951</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46252</v>
+        <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45827</v>
+        <v>46058</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>18.7</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45827</v>
+        <v>46210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3394,14 +3399,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46084</v>
+        <v>46210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3413,13 +3418,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44951</v>
+        <v>46058</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45616</v>
+        <v>44978</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44978</v>
+        <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45534</v>
+        <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45758</v>
+        <v>46218</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45554</v>
+        <v>46223</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44596</v>
+        <v>46223</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45547</v>
+        <v>44978</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44977</v>
+        <v>46084</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4075,8 +4075,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4124,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4138,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45684</v>
+        <v>45173</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4154,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4197,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4211,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45684</v>
+        <v>45545</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4227,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4270,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4284,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45628</v>
+        <v>44951</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4300,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4343,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4357,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45608</v>
+        <v>45068</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4373,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4416,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4421,14 +4426,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44992</v>
+        <v>45098</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4441,7 +4446,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4501,7 +4506,7 @@
         <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4557,7 +4562,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4576,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45219</v>
+        <v>45658</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4592,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4635,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45287</v>
+        <v>45338</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4659,13 +4664,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4708,7 +4708,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45621</v>
+        <v>45314</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45497</v>
+        <v>45628</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44937</v>
+        <v>45404</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45338</v>
+        <v>44977</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45608</v>
+        <v>45758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>14.7</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45068</v>
+        <v>45628</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45545</v>
+        <v>44992</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45545</v>
+        <v>44783</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45631</v>
+        <v>45684</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45658</v>
+        <v>45684</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44816</v>
+        <v>45295</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45607</v>
+        <v>46252</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45225</v>
+        <v>45187</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45187</v>
+        <v>44816</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45173</v>
+        <v>46023</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45314</v>
+        <v>45322</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45237</v>
+        <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45631</v>
+        <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45628</v>
+        <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44887</v>
+        <v>45621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44951</v>
+        <v>45019</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1060,7 +1060,7 @@
         <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44784</v>
+        <v>45628</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46185</v>
+        <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45554</v>
+        <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44837</v>
+        <v>44783</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45454</v>
+        <v>45545</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1510,13 +1510,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1559,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1573,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45545</v>
+        <v>44978</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1632,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1646,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45631</v>
+        <v>44992</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1662,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1705,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44937</v>
+        <v>45019</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1735,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1778,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45287</v>
+        <v>45027</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1807,13 +1802,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1856,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1870,10 +1860,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45608</v>
+        <v>45219</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1886,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>14.7</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1929,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1943,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45225</v>
+        <v>45287</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1958,8 +1948,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2002,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2016,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45608</v>
+        <v>45621</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2032,7 +2027,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2075,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2089,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45545</v>
+        <v>44837</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2105,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2148,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2162,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45547</v>
+        <v>45497</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2178,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2221,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2235,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45631</v>
+        <v>44951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2251,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2294,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44887</v>
+        <v>45454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2323,8 +2318,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2367,7 +2367,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>44978</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44977</v>
+        <v>44937</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45698</v>
+        <v>45338</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45791</v>
+        <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45497</v>
+        <v>45554</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45607</v>
+        <v>44596</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45827</v>
+        <v>45547</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>18.7</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45827</v>
+        <v>45608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>14.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45616</v>
+        <v>45068</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45237</v>
+        <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44951</v>
+        <v>45545</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46205</v>
+        <v>45545</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46058</v>
+        <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46210</v>
+        <v>45632</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46210</v>
+        <v>45658</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46058</v>
+        <v>44816</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44978</v>
+        <v>45607</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45546</v>
+        <v>45698</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46223</v>
+        <v>46210</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46223</v>
+        <v>46210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44978</v>
+        <v>46218</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46084</v>
+        <v>46223</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4075,13 +4075,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4124,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4138,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45173</v>
+        <v>46223</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4154,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4197,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4211,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45545</v>
+        <v>46058</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4227,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4270,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4284,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44951</v>
+        <v>46058</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4300,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4343,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4357,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45068</v>
+        <v>45225</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4373,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4416,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4426,14 +4421,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45098</v>
+        <v>45187</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4446,7 +4441,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4489,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4503,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45027</v>
+        <v>45173</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4519,7 +4514,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45658</v>
+        <v>45314</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4592,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45338</v>
+        <v>45237</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4665,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4708,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4718,14 +4713,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45314</v>
+        <v>46084</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4737,8 +4732,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45404</v>
+        <v>45628</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4927,7 +4927,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44977</v>
+        <v>46252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45758</v>
+        <v>44887</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45628</v>
+        <v>44951</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5156,14 +5156,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44992</v>
+        <v>45098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44783</v>
+        <v>45404</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5302,14 +5302,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45684</v>
+        <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45684</v>
+        <v>45546</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45295</v>
+        <v>45322</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46252</v>
+        <v>44977</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45187</v>
+        <v>45758</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44816</v>
+        <v>45827</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>18.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46023</v>
+        <v>45827</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45322</v>
+        <v>45295</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45534</v>
+        <v>45684</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45219</v>
+        <v>45684</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44596</v>
+        <v>45616</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45621</v>
+        <v>46023</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45019</v>
+        <v>46185</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44784</v>
+        <v>45068</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44723</v>
+        <v>45098</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45628</v>
+        <v>44723</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>44784</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45608</v>
+        <v>45027</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44783</v>
+        <v>45658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45545</v>
+        <v>45338</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1554,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44978</v>
+        <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44992</v>
+        <v>45698</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1700,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45019</v>
+        <v>45628</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45027</v>
+        <v>45404</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1856,14 +1856,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45219</v>
+        <v>45791</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45287</v>
+        <v>44977</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1948,13 +1948,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1997,7 +1992,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2011,10 +2006,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45621</v>
+        <v>45454</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2026,8 +2021,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44837</v>
+        <v>45628</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45497</v>
+        <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44951</v>
+        <v>44783</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45454</v>
+        <v>45827</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2318,13 +2318,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>18.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2367,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2381,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44978</v>
+        <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2397,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44937</v>
+        <v>44837</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45338</v>
+        <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45534</v>
+        <v>45187</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45554</v>
+        <v>45616</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44596</v>
+        <v>44816</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45547</v>
+        <v>45631</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45608</v>
+        <v>45322</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>14.7</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45068</v>
+        <v>45534</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44977</v>
+        <v>45758</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45545</v>
+        <v>45219</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45545</v>
+        <v>45684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45631</v>
+        <v>45684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45632</v>
+        <v>44596</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45658</v>
+        <v>45621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44816</v>
+        <v>45608</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>14.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3560,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46205</v>
+        <v>45019</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3638,7 +3633,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3676,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45698</v>
+        <v>44784</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3706,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46210</v>
+        <v>46023</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46210</v>
+        <v>45554</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46210</v>
+        <v>46185</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46218</v>
+        <v>46058</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46223</v>
+        <v>46058</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46223</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46058</v>
+        <v>45545</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46058</v>
+        <v>44937</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45225</v>
+        <v>44887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4411,7 +4406,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4421,14 +4416,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45187</v>
+        <v>46084</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4440,8 +4435,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45173</v>
+        <v>45287</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4513,8 +4513,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4557,7 +4562,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4571,10 +4576,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45314</v>
+        <v>45225</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4587,7 +4592,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4630,7 +4635,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4644,10 +4649,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45237</v>
+        <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4703,7 +4708,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4713,14 +4718,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46084</v>
+        <v>46210</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4732,13 +4737,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45631</v>
+        <v>46210</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45628</v>
+        <v>45545</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46252</v>
+        <v>46210</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44887</v>
+        <v>45547</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44951</v>
+        <v>44977</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5156,14 +5156,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45098</v>
+        <v>46218</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45404</v>
+        <v>46223</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5302,14 +5302,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45791</v>
+        <v>46223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45546</v>
+        <v>45632</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5438,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45322</v>
+        <v>45497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5511,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44977</v>
+        <v>45607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5584,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45758</v>
+        <v>46252</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45827</v>
+        <v>45237</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>18.7</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5730,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45827</v>
+        <v>44951</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45295</v>
+        <v>44978</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45684</v>
+        <v>45546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45684</v>
+        <v>44978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45616</v>
+        <v>45173</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46023</v>
+        <v>45545</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46185</v>
+        <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>

--- a/Översikt KUMLA.xlsx
+++ b/Översikt KUMLA.xlsx
@@ -601,7 +601,7 @@
         <v>44258</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44879</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45621</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45748</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 21921-2023</t>
+          <t>A 32864-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45068</v>
+        <v>44784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 29680-2023</t>
+          <t>A 24077-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45098</v>
+        <v>44723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 24077-2022</t>
+          <t>A 23648-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44723</v>
+        <v>45454</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1218,8 +1218,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1262,7 +1267,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32864-2022</t>
+          <t>A 57949-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1276,10 +1281,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44784</v>
+        <v>45631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1292,7 +1297,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1335,7 +1340,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 16132-2023</t>
+          <t>A 52192-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45027</v>
+        <v>45608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>14.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1408,7 +1413,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 12-2025</t>
+          <t>A 52180-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45658</v>
+        <v>45608</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1481,7 +1486,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 6315-2024</t>
+          <t>A 57944-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1495,10 +1500,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45338</v>
+        <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1516,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1554,7 +1559,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2653-2024</t>
+          <t>A 55442-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45314</v>
+        <v>44887</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1627,7 +1632,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6266-2025</t>
+          <t>A 23225-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1637,14 +1642,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45698</v>
+        <v>45791</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1657,7 +1662,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1700,7 +1705,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56712-2024</t>
+          <t>A 8612-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45628</v>
+        <v>44977</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1773,7 +1778,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15781-2024</t>
+          <t>A 30806-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45404</v>
+        <v>45497</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1803,7 +1808,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1846,7 +1851,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 23225-2025</t>
+          <t>A 51940-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1856,14 +1861,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45791</v>
+        <v>45607</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1919,7 +1924,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8460-2023</t>
+          <t>A 30465-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1933,10 +1938,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44977</v>
+        <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1949,7 +1954,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>18.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1992,7 +1997,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23648-2024</t>
+          <t>A 43706-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2006,10 +2011,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45454</v>
+        <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2021,13 +2026,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56730-2024</t>
+          <t>A 30466-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45628</v>
+        <v>45827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11141-2023</t>
+          <t>A 54080-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44992</v>
+        <v>45616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32725-2022</t>
+          <t>A 55208-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44783</v>
+        <v>45237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30465-2025</t>
+          <t>A 3872-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45827</v>
+        <v>44951</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>18.7</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30466-2025</t>
+          <t>A 7270-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45827</v>
+        <v>46058</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 43706-2022</t>
+          <t>A 7272-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44837</v>
+        <v>46058</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 323-2024</t>
+          <t>A 8687-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45295</v>
+        <v>44978</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43661-2023</t>
+          <t>A 38615-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45187</v>
+        <v>45546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54080-2024</t>
+          <t>A 8852-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45616</v>
+        <v>44978</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38768-2022</t>
+          <t>A 11683-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2737,14 +2737,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44816</v>
+        <v>46084</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2756,8 +2756,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 57949-2024</t>
+          <t>A 40897-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45631</v>
+        <v>45173</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3920-2024</t>
+          <t>A 38193-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45322</v>
+        <v>45545</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36237-2024</t>
+          <t>A 3873-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45534</v>
+        <v>44951</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17920-2025</t>
+          <t>A 21921-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45758</v>
+        <v>45068</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51239-2023</t>
+          <t>A 29680-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3102,14 +3107,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45219</v>
+        <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4100-2025</t>
+          <t>A 16132-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45684</v>
+        <v>45027</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4102-2025</t>
+          <t>A 12-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45684</v>
+        <v>45658</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3268,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5781-2022</t>
+          <t>A 6315-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44596</v>
+        <v>45338</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55340-2024</t>
+          <t>A 2653-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45621</v>
+        <v>45314</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52192-2024</t>
+          <t>A 56712-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45608</v>
+        <v>45628</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3492,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>14.7</v>
+        <v>0.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52180-2024</t>
+          <t>A 15781-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45608</v>
+        <v>45404</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3560,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15356-2023</t>
+          <t>A 8460-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45019</v>
+        <v>44977</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3633,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3676,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32859-2022</t>
+          <t>A 56730-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44784</v>
+        <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3706,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 601-2026</t>
+          <t>A 11141-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46023</v>
+        <v>44992</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40275-2024</t>
+          <t>A 32725-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45554</v>
+        <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27541-2026</t>
+          <t>A 323-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46185</v>
+        <v>45295</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7270-2026</t>
+          <t>A 17920-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46058</v>
+        <v>45758</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7272-2026</t>
+          <t>A 43661-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46058</v>
+        <v>45187</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57944-2024</t>
+          <t>A 4100-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>45684</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38343-2024</t>
+          <t>A 4102-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45545</v>
+        <v>45684</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1478-2023</t>
+          <t>A 38768-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44937</v>
+        <v>44816</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55442-2022</t>
+          <t>A 3920-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44887</v>
+        <v>45322</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4363,7 +4368,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4406,7 +4411,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11683-2026</t>
+          <t>A 36237-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4416,14 +4421,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46084</v>
+        <v>45534</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4435,13 +4440,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 65076-2023</t>
+          <t>A 51239-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45287</v>
+        <v>45219</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4513,13 +4513,8 @@
           <t>KUMLA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54080-2023</t>
+          <t>A 601-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45225</v>
+        <v>46023</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4592,7 +4587,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29930-2026</t>
+          <t>A 27541-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46205</v>
+        <v>46185</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4665,7 +4660,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4708,7 +4703,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30478-2026</t>
+          <t>A 5781-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4722,10 +4717,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46210</v>
+        <v>44596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4738,7 +4733,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4781,7 +4776,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30475-2026</t>
+          <t>A 55340-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4795,10 +4790,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46210</v>
+        <v>45621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4811,7 +4806,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4854,7 +4849,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38335-2024</t>
+          <t>A 15356-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,10 +4863,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45545</v>
+        <v>45019</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4884,7 +4879,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4927,7 +4922,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30477-2026</t>
+          <t>A 32859-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4941,10 +4936,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46210</v>
+        <v>44784</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4957,7 +4952,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5000,7 +4995,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38871-2024</t>
+          <t>A 29930-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5014,10 +5009,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45547</v>
+        <v>46205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5030,7 +5025,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5073,7 +5068,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8612-2023</t>
+          <t>A 30478-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5087,10 +5082,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44977</v>
+        <v>46210</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5103,7 +5098,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5146,7 +5141,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31294-2026</t>
+          <t>A 30475-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5176,7 +5171,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5219,7 +5214,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31546-2026</t>
+          <t>A 40275-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46223</v>
+        <v>45554</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5249,7 +5244,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5292,7 +5287,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31545-2026</t>
+          <t>A 30477-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5306,10 +5301,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46223</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5322,7 +5317,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5365,7 +5360,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58657-2024</t>
+          <t>A 31294-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5379,10 +5374,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45632</v>
+        <v>46218</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5395,7 +5390,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5438,7 +5433,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30806-2024</t>
+          <t>A 31546-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45497</v>
+        <v>46223</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5468,7 +5463,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5511,7 +5506,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51940-2024</t>
+          <t>A 31545-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5525,10 +5520,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45607</v>
+        <v>46223</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5541,7 +5536,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5584,7 +5579,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34011-2026</t>
+          <t>A 38343-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46252</v>
+        <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5614,7 +5609,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5657,7 +5652,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55208-2023</t>
+          <t>A 1478-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5671,10 +5666,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45237</v>
+        <v>44937</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5730,7 +5725,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3872-2023</t>
+          <t>A 65076-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44951</v>
+        <v>45287</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5759,8 +5754,13 @@
           <t>KUMLA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5803,7 +5803,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8687-2023</t>
+          <t>A 54080-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44978</v>
+        <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38615-2024</t>
+          <t>A 38335-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45546</v>
+        <v>45545</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8852-2023</t>
+          <t>A 38871-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44978</v>
+        <v>45547</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40897-2023</t>
+          <t>A 58657-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45173</v>
+        <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38193-2024</t>
+          <t>A 34011-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45545</v>
+        <v>46252</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3873-2023</t>
+          <t>A 6266-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44951</v>
+        <v>45698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
